--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/FilledTemplates/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/FilledTemplates/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH Matrix" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SH Register'!$B$6:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SH Register'!$B$6:$O$17</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -278,17 +278,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -303,7 +303,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009EDD1E"/>
+        <fgColor rgb="0017B2C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -313,7 +313,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017B2C4"/>
+        <fgColor rgb="009EDD1E"/>
       </patternFill>
     </fill>
   </fills>
@@ -867,9 +867,6 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -889,6 +886,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1363,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="19.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="19.85546875" customWidth="1" style="14" min="1" max="1"/>
@@ -1384,89 +1384,88 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr"/>
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="C1" s="61" t="inlineStr">
+      <c r="C1" s="60" t="inlineStr">
         <is>
           <t>"VNS" — Custom University Learning Platform</t>
         </is>
       </c>
-      <c r="D1" s="62" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="61" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
+      <c r="E1" s="60" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="63" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" s="63" t="inlineStr">
         <is>
           <t>Nazar Zankovych</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="64" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
-        <is>
-          <t>V1.1</t>
+      <c r="E2" s="63" t="inlineStr">
+        <is>
+          <t>V1.2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="63" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Project Sponsor</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University; Ministry of Education and Science of Ukraine</t>
         </is>
       </c>
-      <c r="D3" s="65" t="inlineStr">
+      <c r="D3" s="64" t="inlineStr">
         <is>
           <t>Project Start Date</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr">
+      <c r="E3" s="63" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="63" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Project Phase</t>
         </is>
       </c>
-      <c r="C4" s="64" t="inlineStr">
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>Initiation</t>
         </is>
       </c>
-      <c r="D4" s="65" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
         <is>
           <t>Project End Date</t>
         </is>
       </c>
-      <c r="E4" s="64" t="inlineStr">
+      <c r="E4" s="63" t="inlineStr">
         <is>
           <t>31/01/2027</t>
         </is>
@@ -1475,89 +1474,89 @@
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="13" t="n"/>
-      <c r="D5" s="66" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>Andrii Lysun (Business Analyst)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customFormat="1" customHeight="1" s="16" thickBot="1">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>STAKEHOLDERS</t>
         </is>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C6" s="68" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr">
+      <c r="D6" s="67" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="E6" s="68" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>Role/Job Title</t>
         </is>
       </c>
-      <c r="F6" s="68" t="inlineStr">
+      <c r="F6" s="67" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G6" s="68" t="inlineStr">
+      <c r="G6" s="67" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H6" s="68" t="inlineStr">
+      <c r="H6" s="67" t="inlineStr">
         <is>
           <t>Communication Channel</t>
         </is>
       </c>
-      <c r="I6" s="68" t="inlineStr">
+      <c r="I6" s="67" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="J6" s="68" t="inlineStr">
+      <c r="J6" s="67" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="K6" s="68" t="inlineStr">
+      <c r="K6" s="67" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="L6" s="68" t="inlineStr">
+      <c r="L6" s="67" t="inlineStr">
         <is>
           <t>Power*</t>
         </is>
       </c>
-      <c r="M6" s="68" t="inlineStr">
+      <c r="M6" s="67" t="inlineStr">
         <is>
           <t>Interest*</t>
         </is>
       </c>
-      <c r="N6" s="68" t="inlineStr">
+      <c r="N6" s="67" t="inlineStr">
         <is>
           <t>Approach*</t>
         </is>
       </c>
-      <c r="O6" s="68" t="inlineStr">
+      <c r="O6" s="67" t="inlineStr">
         <is>
           <t>Comments/Notes</t>
         </is>
@@ -1565,79 +1564,79 @@
     </row>
     <row r="7" ht="44" customFormat="1" customHeight="1" s="18" thickBot="1">
       <c r="A7" s="17" t="n"/>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>Full name of the stakeholder</t>
         </is>
       </c>
-      <c r="C7" s="69" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>Internal / External / Primary or Secondary</t>
         </is>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>The name of the organization or group the stakeholder belongs to</t>
         </is>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>Job title or role held by the stakeholder</t>
         </is>
       </c>
-      <c r="F7" s="69" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>Work Email and personal Email, with consent of individual</t>
         </is>
       </c>
-      <c r="G7" s="69" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>Primary + alternative contact info</t>
         </is>
       </c>
-      <c r="H7" s="69" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>Via email, Conference call, Message etc.</t>
         </is>
       </c>
-      <c r="I7" s="69" t="inlineStr">
+      <c r="I7" s="68" t="inlineStr">
         <is>
           <t>The frequency of communication to be done within a pre-defined timeframe</t>
         </is>
       </c>
-      <c r="J7" s="69" t="inlineStr">
+      <c r="J7" s="68" t="inlineStr">
         <is>
           <t>City and Country where the person is located</t>
         </is>
       </c>
-      <c r="K7" s="69" t="inlineStr">
+      <c r="K7" s="68" t="inlineStr">
         <is>
           <t>Time Zone which the person belongs to</t>
         </is>
       </c>
-      <c r="L7" s="69" t="inlineStr">
+      <c r="L7" s="68" t="inlineStr">
         <is>
           <t>High / Low</t>
         </is>
       </c>
-      <c r="M7" s="69" t="inlineStr">
+      <c r="M7" s="68" t="inlineStr">
         <is>
           <t>High / Low</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr">
+      <c r="N7" s="68" t="inlineStr">
         <is>
           <t>Key Player / Keep Informed / Meet their needs etc.</t>
         </is>
       </c>
-      <c r="O7" s="69" t="inlineStr">
+      <c r="O7" s="68" t="inlineStr">
         <is>
           <t>Additional details to keep in mind</t>
         </is>
       </c>
     </row>
     <row r="8" ht="74" customHeight="1">
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University</t>
         </is>
@@ -1647,37 +1646,37 @@
           <t>External / Primary</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>Project Sponsor — customer and owner of the future platform</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="69" t="inlineStr">
         <is>
           <t>office@lpnu.ua</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="G8" s="69" t="inlineStr">
         <is>
           <t>+380 (32) 258-21-11</t>
         </is>
       </c>
-      <c r="H8" s="59" t="inlineStr">
+      <c r="H8" s="69" t="inlineStr">
         <is>
           <t>Meeting + written status report</t>
         </is>
       </c>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="I8" s="69" t="inlineStr">
         <is>
           <t>Every two weeks, Tuesday</t>
         </is>
       </c>
-      <c r="J8" s="59" t="inlineStr">
+      <c r="J8" s="69" t="inlineStr">
         <is>
           <t>Lviv, Ukraine</t>
         </is>
@@ -1702,14 +1701,14 @@
           <t>Key Player</t>
         </is>
       </c>
-      <c r="O8" s="59" t="inlineStr">
-        <is>
-          <t>Funds the project and owns the current VNS platform and the student data. Approves scope and accepts the final result. Main interest is replacing the outdated Moodle-based platform and gaining engagement analytics.</t>
+      <c r="O8" s="69" t="inlineStr">
+        <is>
+          <t>Funds the project, owns the current VNS platform and the student data, and represents the university leadership: approves the project charter and MVP scope and accepts the final result. Main interest is replacing the outdated Moodle-based platform and gaining engagement analytics.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="74" customHeight="1">
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>Ministry of Education and Science of Ukraine</t>
         </is>
@@ -1719,37 +1718,37 @@
           <t>External / Secondary</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>Ministry of Education and Science of Ukraine</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>Project Sponsor — sector regulator and funding source</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>office@mon.gov.ua</t>
         </is>
       </c>
-      <c r="G9" s="59" t="inlineStr">
+      <c r="G9" s="69" t="inlineStr">
         <is>
           <t>+380 (44) 481-32-21</t>
         </is>
       </c>
-      <c r="H9" s="59" t="inlineStr">
-        <is>
-          <t>Monitoring of national regulation</t>
-        </is>
-      </c>
-      <c r="I9" s="59" t="inlineStr">
-        <is>
-          <t>Ad hoc, if regulation changes</t>
-        </is>
-      </c>
-      <c r="J9" s="59" t="inlineStr">
+      <c r="H9" s="69" t="inlineStr">
+        <is>
+          <t>Official one-page report</t>
+        </is>
+      </c>
+      <c r="I9" s="69" t="inlineStr">
+        <is>
+          <t>Once per semester and at control points</t>
+        </is>
+      </c>
+      <c r="J9" s="69" t="inlineStr">
         <is>
           <t>Kyiv, Ukraine</t>
         </is>
@@ -1761,317 +1760,317 @@
       </c>
       <c r="L9" s="70" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="70" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M9" s="70" t="inlineStr">
+      <c r="N9" s="70" t="inlineStr">
+        <is>
+          <t>Meet their needs</t>
+        </is>
+      </c>
+      <c r="O9" s="69" t="inlineStr">
+        <is>
+          <t>Sets the regulatory framework for educational IT systems and for processing personal data in education, and can condition the scaling of the product beyond the pilot. Not involved in day-to-day work: kept satisfied through formal semester reporting and consulted only on decisions with regulatory impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="74" customHeight="1">
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>Technical Department of Lviv Polytechnic</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>External / Secondary</t>
+        </is>
+      </c>
+      <c r="D10" s="69" t="inlineStr">
+        <is>
+          <t>Lviv Polytechnic National University</t>
+        </is>
+      </c>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>Developers and administrators of the current VNS</t>
+        </is>
+      </c>
+      <c r="F10" s="69" t="inlineStr">
+        <is>
+          <t>it.support@lpnu.ua</t>
+        </is>
+      </c>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>+380 (32) 258-21-77</t>
+        </is>
+      </c>
+      <c r="H10" s="69" t="inlineStr">
+        <is>
+          <t>E-mail / ticket on request</t>
+        </is>
+      </c>
+      <c r="I10" s="69" t="inlineStr">
+        <is>
+          <t>As needed (registry export, infrastructure access)</t>
+        </is>
+      </c>
+      <c r="J10" s="69" t="inlineStr">
+        <is>
+          <t>Lviv, Ukraine</t>
+        </is>
+      </c>
+      <c r="K10" s="70" t="inlineStr">
+        <is>
+          <t>EET (UTC+2)</t>
+        </is>
+      </c>
+      <c r="L10" s="70" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N9" s="70" t="inlineStr">
+      <c r="M10" s="70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N10" s="70" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="O9" s="59" t="inlineStr">
-        <is>
-          <t>Formal sponsor of the sector, but for a pilot inside a single department the ministry has neither influence over delivery nor day-to-day interest in it. Monitored only in case the national regulation of educational IT systems changes; no recurring communication and no project activity is assigned to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="74" customHeight="1">
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Nataliia Shakhovska</t>
-        </is>
-      </c>
-      <c r="C10" s="70" t="inlineStr">
+      <c r="O10" s="69" t="inlineStr">
+        <is>
+          <t>Built and maintain the current VNS. Because the project uses its own custom backend with no Moodle integration, the department neither controls delivery nor depends on its result. Involvement is limited to one-off requests: the export of the student registry and access to university infrastructure. Monitored in case they react to the replacement of their system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="74" customHeight="1">
+      <c r="B11" s="69" t="inlineStr">
+        <is>
+          <t>End users — students and lecturers</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
         <is>
           <t>External / Primary</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
-        <is>
-          <t>Rector's Office, Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="E10" s="59" t="inlineStr">
-        <is>
-          <t>Rector of Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="F10" s="59" t="inlineStr">
-        <is>
-          <t>nataliia.b.shakhovska@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="inlineStr">
-        <is>
-          <t>+380 (32) 258-26-00</t>
-        </is>
-      </c>
-      <c r="H10" s="59" t="inlineStr">
-        <is>
-          <t>E-mail with a one-page summary</t>
-        </is>
-      </c>
-      <c r="I10" s="59" t="inlineStr">
-        <is>
-          <t>Once per semester and at control points</t>
-        </is>
-      </c>
-      <c r="J10" s="59" t="inlineStr">
+      <c r="D11" s="69" t="inlineStr">
+        <is>
+          <t>Students and teaching staff of Lviv Polytechnic National University</t>
+        </is>
+      </c>
+      <c r="E11" s="69" t="inlineStr">
+        <is>
+          <t>End users of the product: students and lecturers</t>
+        </is>
+      </c>
+      <c r="F11" s="69" t="inlineStr">
+        <is>
+          <t>Via learning channels and @lpnu.ua mailboxes</t>
+        </is>
+      </c>
+      <c r="G11" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="69" t="inlineStr">
+        <is>
+          <t>Interviews, surveys, usability tests, demos</t>
+        </is>
+      </c>
+      <c r="I11" s="69" t="inlineStr">
+        <is>
+          <t>Weekly during elicitation and the pilot</t>
+        </is>
+      </c>
+      <c r="J11" s="69" t="inlineStr">
         <is>
           <t>Lviv, Ukraine</t>
         </is>
       </c>
-      <c r="K10" s="70" t="inlineStr">
+      <c r="K11" s="70" t="inlineStr">
         <is>
           <t>EET (UTC+2)</t>
         </is>
       </c>
-      <c r="L10" s="70" t="inlineStr">
+      <c r="L11" s="70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" s="70" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="70" t="inlineStr">
+      <c r="N11" s="70" t="inlineStr">
+        <is>
+          <t>Keep Informed</t>
+        </is>
+      </c>
+      <c r="O11" s="69" t="inlineStr">
+        <is>
+          <t>Primary target audience in two roles. Students: scattered chats, misleading grade summary, empty calendar. Lecturers: course materials, assignments, activity analytics and the AI mode for graded work. No direct influence on decisions, but requirements not validated with them will be wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="74" customHeight="1">
+      <c r="B12" s="71" t="inlineStr">
+        <is>
+          <t>Kostiantyn Holovskyi</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="inlineStr">
+        <is>
+          <t>Internal / Primary</t>
+        </is>
+      </c>
+      <c r="D12" s="71" t="inlineStr">
+        <is>
+          <t>Project team “20/80”</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="F12" s="71" t="inlineStr">
+        <is>
+          <t>kostiantyn.holovskyi.shi.2025@lpnu.ua</t>
+        </is>
+      </c>
+      <c r="G12" s="71" t="inlineStr">
+        <is>
+          <t>+380 (67) 000-00-01</t>
+        </is>
+      </c>
+      <c r="H12" s="71" t="inlineStr">
+        <is>
+          <t>Team meeting + backlog</t>
+        </is>
+      </c>
+      <c r="I12" s="71" t="inlineStr">
+        <is>
+          <t>Weekly, Monday</t>
+        </is>
+      </c>
+      <c r="J12" s="71" t="inlineStr">
+        <is>
+          <t>Lviv, Ukraine</t>
+        </is>
+      </c>
+      <c r="K12" s="72" t="inlineStr">
+        <is>
+          <t>EET (UTC+2)</t>
+        </is>
+      </c>
+      <c r="L12" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N12" s="72" t="inlineStr">
+        <is>
+          <t>Key Player</t>
+        </is>
+      </c>
+      <c r="O12" s="71" t="inlineStr">
+        <is>
+          <t>Owns the product vision and backlog priorities. Approves the MVP scope and accepts the result from the product side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="74" customHeight="1">
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>Nazar Zankovych</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
+        <is>
+          <t>Internal / Primary</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
+        <is>
+          <t>Project team “20/80”</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="inlineStr">
+        <is>
+          <t>nazar.zankovych.shi.2025@lpnu.ua</t>
+        </is>
+      </c>
+      <c r="G13" s="71" t="inlineStr">
+        <is>
+          <t>+380 (67) 000-00-02</t>
+        </is>
+      </c>
+      <c r="H13" s="71" t="inlineStr">
+        <is>
+          <t>All project ceremonies</t>
+        </is>
+      </c>
+      <c r="I13" s="71" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="J13" s="71" t="inlineStr">
+        <is>
+          <t>Lviv, Ukraine</t>
+        </is>
+      </c>
+      <c r="K13" s="72" t="inlineStr">
+        <is>
+          <t>EET (UTC+2)</t>
+        </is>
+      </c>
+      <c r="L13" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="72" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N10" s="70" t="inlineStr">
+      <c r="N13" s="72" t="inlineStr">
         <is>
           <t>Meet their needs</t>
         </is>
       </c>
-      <c r="O10" s="59" t="inlineStr">
-        <is>
-          <t>Highest decision-making authority in the university: approves the project charter and is the person who can authorise scaling the product beyond the pilot. Not involved day to day — summary communication only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="74" customHeight="1">
-      <c r="B11" s="59" t="inlineStr">
-        <is>
-          <t>Nataliia Boiko</t>
-        </is>
-      </c>
-      <c r="C11" s="70" t="inlineStr">
-        <is>
-          <t>External / Primary</t>
-        </is>
-      </c>
-      <c r="D11" s="59" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="E11" s="59" t="inlineStr">
-        <is>
-          <t>Lecturer — customer and end user</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="inlineStr">
-        <is>
-          <t>nataliia.i.boiko@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>+380 (32) 258-25-30</t>
-        </is>
-      </c>
-      <c r="H11" s="59" t="inlineStr">
-        <is>
-          <t>Interview, requirements workshop, increment demo</t>
-        </is>
-      </c>
-      <c r="I11" s="59" t="inlineStr">
-        <is>
-          <t>Weekly, Thursday</t>
-        </is>
-      </c>
-      <c r="J11" s="59" t="inlineStr">
-        <is>
-          <t>Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="K11" s="70" t="inlineStr">
-        <is>
-          <t>EET (UTC+2)</t>
-        </is>
-      </c>
-      <c r="L11" s="70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M11" s="70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N11" s="70" t="inlineStr">
-        <is>
-          <t>Key Player</t>
-        </is>
-      </c>
-      <c r="O11" s="59" t="inlineStr">
-        <is>
-          <t>Dual role: defines and accepts requirements while also being a future user of the product. Key source of lecturer-facing requirements — course materials, assignments, activity analytics, and the AI mode for graded work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="74" customHeight="1">
-      <c r="B12" s="59" t="inlineStr">
-        <is>
-          <t>Technical Department of Lviv Polytechnic</t>
-        </is>
-      </c>
-      <c r="C12" s="70" t="inlineStr">
-        <is>
-          <t>External / Primary</t>
-        </is>
-      </c>
-      <c r="D12" s="59" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Developers and administrators of the current VNS</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="inlineStr">
-        <is>
-          <t>it.support@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="inlineStr">
-        <is>
-          <t>+380 (32) 258-21-77</t>
-        </is>
-      </c>
-      <c r="H12" s="59" t="inlineStr">
-        <is>
-          <t>Working meeting + e-mail</t>
-        </is>
-      </c>
-      <c r="I12" s="59" t="inlineStr">
-        <is>
-          <t>Every two weeks</t>
-        </is>
-      </c>
-      <c r="J12" s="59" t="inlineStr">
-        <is>
-          <t>Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="K12" s="70" t="inlineStr">
-        <is>
-          <t>EET (UTC+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M12" s="70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N12" s="70" t="inlineStr">
-        <is>
-          <t>Key Player</t>
-        </is>
-      </c>
-      <c r="O12" s="59" t="inlineStr">
-        <is>
-          <t>Own the current VNS, the infrastructure and the student registry, without which registration cannot work. Risk of resistance: the project replaces the system they built — engage them as partners rather than as a supplier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="74" customHeight="1">
-      <c r="B13" s="59" t="inlineStr">
-        <is>
-          <t>End users — Lviv Polytechnic students</t>
-        </is>
-      </c>
-      <c r="C13" s="70" t="inlineStr">
-        <is>
-          <t>External / Primary</t>
-        </is>
-      </c>
-      <c r="D13" s="59" t="inlineStr">
-        <is>
-          <t>Student body of Lviv Polytechnic National University</t>
-        </is>
-      </c>
-      <c r="E13" s="59" t="inlineStr">
-        <is>
-          <t>End users of the product</t>
-        </is>
-      </c>
-      <c r="F13" s="59" t="inlineStr">
-        <is>
-          <t>Via learning channels and @lpnu.ua mailboxes</t>
-        </is>
-      </c>
-      <c r="G13" s="59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="59" t="inlineStr">
-        <is>
-          <t>Survey, usability test, announcement</t>
-        </is>
-      </c>
-      <c r="I13" s="59" t="inlineStr">
-        <is>
-          <t>Weekly during the pilot</t>
-        </is>
-      </c>
-      <c r="J13" s="59" t="inlineStr">
-        <is>
-          <t>Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="K13" s="70" t="inlineStr">
-        <is>
-          <t>EET (UTC+2)</t>
-        </is>
-      </c>
-      <c r="L13" s="70" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M13" s="70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N13" s="70" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="O13" s="59" t="inlineStr">
-        <is>
-          <t>Primary target audience. Source of evidence on the real pain points: scattered chats, misleading grade summary, empty calendar. No direct influence on decisions, but requirements not validated with them will be wrong.</t>
+      <c r="O13" s="71" t="inlineStr">
+        <is>
+          <t>High authority over the plan, schedule, resources and communications. Interest is in delivering on time and within scope rather than in the functional content of the product, which is owned by the Product Owner. Single point of contact for the sponsors.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="74" customHeight="1">
       <c r="B14" s="71" t="inlineStr">
         <is>
-          <t>Kostiantyn Holovskyi</t>
+          <t>Andrii Lysun</t>
         </is>
       </c>
       <c r="C14" s="72" t="inlineStr">
@@ -2086,27 +2085,27 @@
       </c>
       <c r="E14" s="71" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="F14" s="71" t="inlineStr">
         <is>
-          <t>kostiantyn.holovskyi.shi.2025@lpnu.ua</t>
+          <t>andrii.lysun.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="G14" s="71" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-01</t>
+          <t>+380 (67) 000-00-03</t>
         </is>
       </c>
       <c r="H14" s="71" t="inlineStr">
         <is>
-          <t>Team meeting + backlog</t>
+          <t>Requirements elicitation meetings, workshops</t>
         </is>
       </c>
       <c r="I14" s="71" t="inlineStr">
         <is>
-          <t>Weekly, Monday</t>
+          <t>Weekly + as needed</t>
         </is>
       </c>
       <c r="J14" s="71" t="inlineStr">
@@ -2136,14 +2135,14 @@
       </c>
       <c r="O14" s="71" t="inlineStr">
         <is>
-          <t>Owns the product vision and backlog priorities. Approves the MVP scope and accepts the result from the product side.</t>
+          <t>Elicits and documents requirements and produces the BA artifacts and UML models. Main contact for the end users — both students and lecturers.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="74" customHeight="1">
       <c r="B15" s="71" t="inlineStr">
         <is>
-          <t>Nazar Zankovych</t>
+          <t>Denys Lunhul</t>
         </is>
       </c>
       <c r="C15" s="72" t="inlineStr">
@@ -2158,27 +2157,27 @@
       </c>
       <c r="E15" s="71" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Tech Lead, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="F15" s="71" t="inlineStr">
         <is>
-          <t>nazar.zankovych.shi.2025@lpnu.ua</t>
+          <t>denys.lunhul.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="G15" s="71" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-02</t>
+          <t>+380 (67) 000-00-04</t>
         </is>
       </c>
       <c r="H15" s="71" t="inlineStr">
         <is>
-          <t>All project ceremonies</t>
+          <t>Technical sync + code review</t>
         </is>
       </c>
       <c r="I15" s="71" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly, Tuesday</t>
         </is>
       </c>
       <c r="J15" s="71" t="inlineStr">
@@ -2208,19 +2207,19 @@
       </c>
       <c r="O15" s="71" t="inlineStr">
         <is>
-          <t>Responsible for the plan, schedule and communications. Single point of contact for the sponsors, the Rector's office and the Technical Department.</t>
+          <t>Software engineer who also leads the technical side: owns the custom backend architecture, decides on the technology stack and is accountable for the technical feasibility of requirements.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="74" customHeight="1">
       <c r="B16" s="71" t="inlineStr">
         <is>
-          <t>Andrii Lysun</t>
+          <t>Yaroslav Shevchuk</t>
         </is>
       </c>
       <c r="C16" s="72" t="inlineStr">
         <is>
-          <t>Internal / Primary</t>
+          <t>Internal / Secondary</t>
         </is>
       </c>
       <c r="D16" s="71" t="inlineStr">
@@ -2230,27 +2229,27 @@
       </c>
       <c r="E16" s="71" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>DevOps, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="F16" s="71" t="inlineStr">
         <is>
-          <t>andrii.lysun.shi.2025@lpnu.ua</t>
+          <t>yaroslav.shevchuk.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="G16" s="71" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-03</t>
+          <t>+380 (67) 000-00-05</t>
         </is>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>Requirements elicitation meetings, workshops</t>
+          <t>Daily stand-up + technical sync</t>
         </is>
       </c>
       <c r="I16" s="71" t="inlineStr">
         <is>
-          <t>Weekly + as needed</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="J16" s="71" t="inlineStr">
@@ -2265,34 +2264,34 @@
       </c>
       <c r="L16" s="72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M16" s="72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N16" s="72" t="inlineStr">
         <is>
-          <t>Key Player</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="O16" s="71" t="inlineStr">
         <is>
-          <t>Elicits and documents requirements and produces the BA artifacts and UML models. Main contact for Nataliia Boiko and the end users.</t>
+          <t>Software engineer who also owns deployment, environments and CI/CD. Low influence: executes tasks agreed in planning and does not set scope or priorities. Low interest in the business outcome: engagement is at task level. Kept in the loop through the team's own ceremonies, so no separate stakeholder communication is needed.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="74" customHeight="1">
       <c r="B17" s="71" t="inlineStr">
         <is>
-          <t>Denys Lunhul</t>
+          <t>Volodymyr Kamelchuk</t>
         </is>
       </c>
       <c r="C17" s="72" t="inlineStr">
         <is>
-          <t>Internal / Primary</t>
+          <t>Internal / Secondary</t>
         </is>
       </c>
       <c r="D17" s="71" t="inlineStr">
@@ -2302,27 +2301,27 @@
       </c>
       <c r="E17" s="71" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>QA Specialist, Software Engineer (SWE)</t>
         </is>
       </c>
       <c r="F17" s="71" t="inlineStr">
         <is>
-          <t>denys.lunhul.shi.2025@lpnu.ua</t>
+          <t>volodymyr.kamelchuk.shi.2025@lpnu.ua</t>
         </is>
       </c>
       <c r="G17" s="71" t="inlineStr">
         <is>
-          <t>+380 (67) 000-00-04</t>
+          <t>+380 (67) 000-00-06</t>
         </is>
       </c>
       <c r="H17" s="71" t="inlineStr">
         <is>
-          <t>Technical sync + code review</t>
+          <t>Daily stand-up + defect report</t>
         </is>
       </c>
       <c r="I17" s="71" t="inlineStr">
         <is>
-          <t>Weekly, Tuesday</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="J17" s="71" t="inlineStr">
@@ -2337,245 +2336,101 @@
       </c>
       <c r="L17" s="72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M17" s="72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N17" s="72" t="inlineStr">
         <is>
-          <t>Key Player</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="O17" s="71" t="inlineStr">
         <is>
-          <t>Responsible for the custom backend architecture and the technical feasibility of requirements. Decides on the technology stack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="74" customHeight="1">
-      <c r="B18" s="71" t="inlineStr">
-        <is>
-          <t>Yaroslav Shevchuk</t>
-        </is>
-      </c>
-      <c r="C18" s="72" t="inlineStr">
-        <is>
-          <t>Internal / Secondary</t>
-        </is>
-      </c>
-      <c r="D18" s="71" t="inlineStr">
-        <is>
-          <t>Project team “20/80”</t>
-        </is>
-      </c>
-      <c r="E18" s="71" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="F18" s="71" t="inlineStr">
-        <is>
-          <t>yaroslav.shevchuk.shi.2025@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="G18" s="71" t="inlineStr">
-        <is>
-          <t>+380 (67) 000-00-05</t>
-        </is>
-      </c>
-      <c r="H18" s="71" t="inlineStr">
-        <is>
-          <t>Daily stand-up + technical sync</t>
-        </is>
-      </c>
-      <c r="I18" s="71" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="J18" s="71" t="inlineStr">
-        <is>
-          <t>Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="K18" s="72" t="inlineStr">
-        <is>
-          <t>EET (UTC+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="72" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M18" s="72" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N18" s="72" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="O18" s="71" t="inlineStr">
-        <is>
-          <t>Deployment, environments, CI/CD, queue and workers for AI tasks. Main contact with the university Technical Department.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="B19" s="71" t="inlineStr">
-        <is>
-          <t>Volodymyr Kamelchuk</t>
-        </is>
-      </c>
-      <c r="C19" s="72" t="inlineStr">
-        <is>
-          <t>Internal / Secondary</t>
-        </is>
-      </c>
-      <c r="D19" s="71" t="inlineStr">
-        <is>
-          <t>Project team “20/80”</t>
-        </is>
-      </c>
-      <c r="E19" s="71" t="inlineStr">
-        <is>
-          <t>QA Specialist</t>
-        </is>
-      </c>
-      <c r="F19" s="71" t="inlineStr">
-        <is>
-          <t>volodymyr.kamelchuk.shi.2025@lpnu.ua</t>
-        </is>
-      </c>
-      <c r="G19" s="71" t="inlineStr">
-        <is>
-          <t>+380 (67) 000-00-06</t>
-        </is>
-      </c>
-      <c r="H19" s="71" t="inlineStr">
-        <is>
-          <t>Daily stand-up + defect report</t>
-        </is>
-      </c>
-      <c r="I19" s="71" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="J19" s="71" t="inlineStr">
-        <is>
-          <t>Lviv, Ukraine</t>
-        </is>
-      </c>
-      <c r="K19" s="72" t="inlineStr">
-        <is>
-          <t>EET (UTC+2)</t>
-        </is>
-      </c>
-      <c r="L19" s="72" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M19" s="72" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N19" s="72" t="inlineStr">
-        <is>
-          <t>Keep Informed</t>
-        </is>
-      </c>
-      <c r="O19" s="71" t="inlineStr">
-        <is>
-          <t>Verifies the acceptance criteria, in particular the correctness of the grade forecast and the AI's refusal to produce complete solutions for graded work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="73" t="inlineStr">
+          <t>Software engineer who also verifies the acceptance criteria, in particular the grade forecast and the AI's refusal to produce complete solutions for graded work. Low influence and low interest in the business outcome; kept in the loop through the team's own ceremonies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="C21" s="74" t="n"/>
-      <c r="D21" s="74" t="n"/>
-      <c r="E21" s="74" t="n"/>
-      <c r="F21" s="74" t="n"/>
-      <c r="G21" s="74" t="n"/>
-      <c r="H21" s="74" t="n"/>
-      <c r="I21" s="74" t="n"/>
-      <c r="J21" s="74" t="n"/>
-      <c r="K21" s="74" t="n"/>
-      <c r="L21" s="74" t="n"/>
-      <c r="M21" s="74" t="n"/>
-      <c r="N21" s="74" t="n"/>
-      <c r="O21" s="75" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="74" t="n"/>
+      <c r="K19" s="74" t="n"/>
+      <c r="L19" s="74" t="n"/>
+      <c r="M19" s="74" t="n"/>
+      <c r="N19" s="74" t="n"/>
+      <c r="O19" s="75" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>Internal — a member of the delivery team; External — a stakeholder on the university or state side. Primary — directly involved; Secondary — involved indirectly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>Power* / Interest*</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>Power — the ability to affect scope, schedule and the decision to launch. Interest — how far the outcome affects the stakeholder's daily work or study. Values: High / Low.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="76" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C22" s="59" t="inlineStr">
-        <is>
-          <t>Internal — a member of the delivery team; External — a stakeholder on the university or state side. Primary — directly involved; Secondary — involved indirectly.</t>
+          <t>Approach*</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>High+High = Key Player (ENGAGE); High+Low = Meet their needs (SATISFY); Low+High = Keep Informed (INFORM); Low+Low = Monitor (MONITOR).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="76" t="inlineStr">
         <is>
-          <t>Power* / Interest*</t>
-        </is>
-      </c>
-      <c r="C23" s="59" t="inlineStr">
-        <is>
-          <t>Power — the ability to affect scope, schedule and the decision to launch. Interest — how far the outcome affects the stakeholder's daily work or study. Values: High / Low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="76" t="inlineStr">
-        <is>
-          <t>Approach*</t>
-        </is>
-      </c>
-      <c r="C24" s="59" t="inlineStr">
-        <is>
-          <t>High+High = Key Player (ENGAGE); High+Low = Meet their needs (SATISFY); Low+High = Keep Informed (INFORM); Low+Low = Monitor (MONITOR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="76" t="inlineStr">
-        <is>
           <t>Contact details</t>
         </is>
       </c>
-      <c r="C25" s="59" t="inlineStr">
+      <c r="C23" s="69" t="inlineStr">
         <is>
           <t>Phone numbers are illustrative placeholders for this training project. Team e-mail addresses follow the real Lviv Polytechnic National University format.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B6:O19"/>
+  <autoFilter ref="B6:O17"/>
   <mergeCells count="5">
     <mergeCell ref="C22:O22"/>
-    <mergeCell ref="B21:O21"/>
     <mergeCell ref="C23:O23"/>
-    <mergeCell ref="C25:O25"/>
-    <mergeCell ref="C24:O24"/>
+    <mergeCell ref="C20:O20"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="C21:O21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1"/>
@@ -2593,17 +2448,16 @@
   <cols>
     <col width="26" customWidth="1" style="4" min="1" max="1"/>
     <col width="72" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="6.6" customWidth="1" style="5" min="3" max="16384"/>
-    <col width="6.6" customWidth="1" min="4" max="4"/>
-    <col width="6.6" customWidth="1" min="5" max="5"/>
-    <col width="6.6" customWidth="1" min="6" max="6"/>
-    <col width="6.6" customWidth="1" min="7" max="7"/>
-    <col width="6.6" customWidth="1" min="8" max="8"/>
-    <col width="6.6" customWidth="1" min="9" max="9"/>
-    <col width="6.6" customWidth="1" min="10" max="10"/>
-    <col width="6.6" customWidth="1" min="11" max="11"/>
-    <col width="6.6" customWidth="1" min="12" max="12"/>
-    <col width="6.6" customWidth="1" min="13" max="13"/>
+    <col width="6.8" customWidth="1" style="5" min="3" max="16384"/>
+    <col width="6.8" customWidth="1" min="4" max="4"/>
+    <col width="6.8" customWidth="1" min="5" max="5"/>
+    <col width="6.8" customWidth="1" min="6" max="6"/>
+    <col width="6.8" customWidth="1" min="7" max="7"/>
+    <col width="6.8" customWidth="1" min="8" max="8"/>
+    <col width="6.8" customWidth="1" min="9" max="9"/>
+    <col width="6.8" customWidth="1" min="10" max="10"/>
+    <col width="6.8" customWidth="1" min="11" max="11"/>
+    <col width="6.8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" thickBot="1">
@@ -2683,7 +2537,7 @@
       </c>
       <c r="D6" s="89" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Executive Sponsor, Rector)</t>
+          <t>Ministry of Education and Science (Sponsor, regulator)</t>
         </is>
       </c>
       <c r="E6" s="89" t="inlineStr">
@@ -2703,34 +2557,30 @@
       </c>
       <c r="H6" s="89" t="inlineStr">
         <is>
-          <t>Tech Lead (D. Lunhul)</t>
+          <t>Tech Lead / SWE (D. Lunhul)</t>
         </is>
       </c>
       <c r="I6" s="89" t="inlineStr">
         <is>
-          <t>DevOps (Y. Shevchuk)</t>
+          <t>DevOps / SWE (Y. Shevchuk)</t>
         </is>
       </c>
       <c r="J6" s="89" t="inlineStr">
         <is>
-          <t>QA Specialist (V. Kamelchuk)</t>
+          <t>QA / SWE (V. Kamelchuk)</t>
         </is>
       </c>
       <c r="K6" s="89" t="inlineStr">
         <is>
-          <t>Nataliia Boiko (Customer / End user)</t>
+          <t>Technical Department of Lviv Polytechnic</t>
         </is>
       </c>
       <c r="L6" s="89" t="inlineStr">
         <is>
-          <t>Technical Department of Lviv Polytechnic</t>
-        </is>
-      </c>
-      <c r="M6" s="89" t="inlineStr">
-        <is>
-          <t>End users — students</t>
-        </is>
-      </c>
+          <t>End users — students and lecturers</t>
+        </is>
+      </c>
+      <c r="M6" s="29" t="n"/>
       <c r="N6" s="29" t="n"/>
       <c r="O6" s="29" t="n"/>
       <c r="P6" s="54" t="n"/>
@@ -2773,56 +2623,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D8" s="95" t="inlineStr">
+      <c r="D8" s="69" t="n"/>
+      <c r="E8" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G8" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H8" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E8" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F8" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G8" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H8" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I8" s="95" t="inlineStr">
+      <c r="J8" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J8" s="95" t="inlineStr">
+      <c r="K8" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K8" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L8" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M8" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L8" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M8" s="36" t="n"/>
       <c r="N8" s="36" t="n"/>
       <c r="O8" s="36" t="n"/>
     </row>
@@ -2833,61 +2675,49 @@
           <t>Identify and analyse stakeholders (register, power/interest matrix)</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D9" s="95" t="inlineStr">
+      <c r="C9" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E9" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F9" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G9" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H9" s="95" t="inlineStr">
+      <c r="I9" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="I9" s="95" t="inlineStr">
+      <c r="J9" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J9" s="95" t="inlineStr">
+      <c r="K9" s="69" t="n"/>
+      <c r="L9" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K9" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L9" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M9" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M9" s="32" t="n"/>
       <c r="N9" s="32" t="n"/>
       <c r="O9" s="32" t="n"/>
     </row>
@@ -2903,56 +2733,48 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D10" s="95" t="inlineStr">
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F10" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G10" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I10" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E10" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F10" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H10" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I10" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J10" s="95" t="inlineStr">
+      <c r="K10" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K10" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="L10" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M10" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
+      <c r="M10" s="32" t="n"/>
       <c r="N10" s="32" t="n"/>
       <c r="O10" s="32" t="n"/>
     </row>
@@ -2963,61 +2785,53 @@
           <t>Develop the business case and the success metrics</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D11" s="95" t="inlineStr">
+      <c r="C11" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H11" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I11" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E11" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G11" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H11" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I11" s="95" t="inlineStr">
+      <c r="J11" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J11" s="95" t="inlineStr">
+      <c r="K11" s="69" t="n"/>
+      <c r="L11" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K11" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M11" s="32" t="n"/>
       <c r="N11" s="32" t="n"/>
       <c r="O11" s="32" t="n"/>
     </row>
@@ -3028,61 +2842,53 @@
           <t>Approve the project charter and the MVP scope</t>
         </is>
       </c>
-      <c r="C12" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D12" s="94" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E12" s="96" t="inlineStr">
+      <c r="D12" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F12" s="96" t="inlineStr">
+      <c r="F12" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G12" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H12" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I12" s="95" t="inlineStr">
+      <c r="G12" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J12" s="95" t="inlineStr">
+      <c r="J12" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K12" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L12" s="95" t="inlineStr">
+      <c r="K12" s="69" t="n"/>
+      <c r="L12" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M12" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M12" s="32" t="n"/>
       <c r="N12" s="32" t="n"/>
       <c r="O12" s="32" t="n"/>
     </row>
@@ -3094,23 +2900,23 @@
       </c>
       <c r="B13" s="93" t="inlineStr">
         <is>
-          <t>Elicit and document requirements (customer interviews, end-user surveys)</t>
-        </is>
-      </c>
-      <c r="C13" s="95" t="inlineStr">
+          <t>Elicit and document requirements (interviews with lecturers, student surveys)</t>
+        </is>
+      </c>
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D13" s="59" t="n"/>
-      <c r="E13" s="97" t="inlineStr">
+      <c r="D13" s="69" t="n"/>
+      <c r="E13" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F13" s="97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G13" s="94" t="inlineStr">
@@ -3118,36 +2924,28 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="H13" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I13" s="95" t="inlineStr">
+      <c r="H13" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I13" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J13" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K13" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L13" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M13" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J13" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="n"/>
       <c r="N13" s="32" t="n"/>
       <c r="O13" s="32" t="n"/>
     </row>
@@ -3158,57 +2956,45 @@
           <t>Build UML models (use case, activity) for the product scenarios</t>
         </is>
       </c>
-      <c r="C14" s="95" t="inlineStr">
+      <c r="C14" s="69" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F14" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D14" s="59" t="n"/>
-      <c r="E14" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F14" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="G14" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="H14" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I14" s="95" t="inlineStr">
+      <c r="H14" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I14" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J14" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K14" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L14" s="95" t="inlineStr">
+      <c r="J14" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" s="69" t="n"/>
+      <c r="L14" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M14" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M14" s="32" t="n"/>
       <c r="N14" s="32" t="n"/>
       <c r="O14" s="32" t="n"/>
     </row>
@@ -3219,23 +3005,19 @@
           <t>Design the data model and the custom backend architecture</t>
         </is>
       </c>
-      <c r="C15" s="95" t="inlineStr">
+      <c r="C15" s="69" t="n"/>
+      <c r="D15" s="69" t="n"/>
+      <c r="E15" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D15" s="59" t="n"/>
-      <c r="E15" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F15" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G15" s="97" t="inlineStr">
+      <c r="G15" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3245,27 +3027,19 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="I15" s="96" t="inlineStr">
+      <c r="I15" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J15" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L15" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M15" s="59" t="n"/>
+      <c r="J15" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="69" t="n"/>
+      <c r="L15" s="69" t="n"/>
+      <c r="M15" s="32" t="n"/>
       <c r="N15" s="32" t="n"/>
       <c r="O15" s="32" t="n"/>
     </row>
@@ -3281,56 +3055,52 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D16" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E16" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F16" s="96" t="inlineStr">
+      <c r="D16" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G16" s="96" t="inlineStr">
+      <c r="G16" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H16" s="97" t="inlineStr">
+      <c r="H16" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="I16" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J16" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
+      <c r="J16" s="97" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K16" s="97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L16" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M16" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
+      <c r="M16" s="32" t="n"/>
       <c r="N16" s="32" t="n"/>
       <c r="O16" s="32" t="n"/>
     </row>
@@ -3341,61 +3111,45 @@
           <t>Produce the communications plan and the project schedule</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D17" s="95" t="inlineStr">
+      <c r="C17" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" s="69" t="n"/>
+      <c r="E17" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="94" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H17" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I17" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E17" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F17" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G17" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H17" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I17" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="J17" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K17" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L17" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M17" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="K17" s="69" t="n"/>
+      <c r="L17" s="69" t="n"/>
+      <c r="M17" s="32" t="n"/>
       <c r="N17" s="32" t="n"/>
       <c r="O17" s="32" t="n"/>
     </row>
@@ -3406,57 +3160,45 @@
           <t>Select the technology stack and the LLM API provider</t>
         </is>
       </c>
-      <c r="C18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D18" s="95" t="inlineStr">
+      <c r="C18" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="69" t="n"/>
+      <c r="E18" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F18" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G18" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="H18" s="94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I18" s="96" t="inlineStr">
+      <c r="I18" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K18" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L18" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M18" s="59" t="n"/>
+      <c r="J18" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K18" s="69" t="n"/>
+      <c r="L18" s="69" t="n"/>
+      <c r="M18" s="32" t="n"/>
       <c r="N18" s="32" t="n"/>
       <c r="O18" s="32" t="n"/>
     </row>
@@ -3471,57 +3213,53 @@
           <t>Obtain the student registry; implement registration and authentication</t>
         </is>
       </c>
-      <c r="C19" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D19" s="59" t="n"/>
-      <c r="E19" s="97" t="inlineStr">
+      <c r="C19" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="69" t="n"/>
+      <c r="E19" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F19" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G19" s="97" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G19" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="H19" s="94" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I19" s="96" t="inlineStr">
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="I19" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J19" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="J19" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="K19" s="95" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L19" s="97" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L19" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M19" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M19" s="32" t="n"/>
       <c r="N19" s="32" t="n"/>
       <c r="O19" s="32" t="n"/>
     </row>
@@ -3532,23 +3270,19 @@
           <t>Implement courses, materials, deadlines and grade forecasting</t>
         </is>
       </c>
-      <c r="C20" s="95" t="inlineStr">
+      <c r="C20" s="69" t="n"/>
+      <c r="D20" s="69" t="n"/>
+      <c r="E20" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D20" s="59" t="n"/>
-      <c r="E20" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G20" s="97" t="inlineStr">
+      <c r="G20" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3560,29 +3294,21 @@
       </c>
       <c r="I20" s="95" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J20" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K20" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J20" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K20" s="69" t="n"/>
+      <c r="L20" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M20" s="32" t="n"/>
       <c r="N20" s="32" t="n"/>
       <c r="O20" s="32" t="n"/>
     </row>
@@ -3593,23 +3319,19 @@
           <t>Implement the communication hub and Study Spaces</t>
         </is>
       </c>
-      <c r="C21" s="95" t="inlineStr">
+      <c r="C21" s="69" t="n"/>
+      <c r="D21" s="69" t="n"/>
+      <c r="E21" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D21" s="59" t="n"/>
-      <c r="E21" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G21" s="97" t="inlineStr">
+      <c r="G21" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3619,31 +3341,23 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="I21" s="96" t="inlineStr">
+      <c r="I21" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J21" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K21" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L21" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M21" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J21" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K21" s="69" t="n"/>
+      <c r="L21" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M21" s="32" t="n"/>
       <c r="N21" s="32" t="n"/>
       <c r="O21" s="32" t="n"/>
     </row>
@@ -3654,57 +3368,49 @@
           <t>Implement the AI assistant: summaries, quizzes, “Ask the course”</t>
         </is>
       </c>
-      <c r="C22" s="95" t="inlineStr">
+      <c r="C22" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D22" s="59" t="n"/>
+      <c r="D22" s="69" t="n"/>
       <c r="E22" s="94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="95" t="inlineStr">
+      <c r="F22" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G22" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H22" s="96" t="inlineStr">
+      <c r="G22" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H22" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I22" s="96" t="inlineStr">
+      <c r="I22" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J22" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K22" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L22" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M22" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J22" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K22" s="69" t="n"/>
+      <c r="L22" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M22" s="32" t="n"/>
       <c r="N22" s="32" t="n"/>
       <c r="O22" s="32" t="n"/>
     </row>
@@ -3715,240 +3421,204 @@
           <t>Set up environments and configure CI/CD</t>
         </is>
       </c>
-      <c r="C23" s="95" t="inlineStr">
+      <c r="C23" s="69" t="n"/>
+      <c r="D23" s="69" t="n"/>
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D23" s="59" t="n"/>
-      <c r="E23" s="95" t="inlineStr">
+      <c r="F23" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F23" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G23" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H23" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I23" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="J23" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K23" s="59" t="n"/>
-      <c r="L23" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M23" s="59" t="n"/>
+      <c r="G23" s="69" t="n"/>
+      <c r="H23" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J23" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K23" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L23" s="69" t="n"/>
+      <c r="M23" s="32" t="n"/>
       <c r="N23" s="32" t="n"/>
       <c r="O23" s="32" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="99" t="n"/>
+      <c r="A24" s="98" t="n"/>
       <c r="B24" s="93" t="inlineStr">
         <is>
           <t>Run testing and acceptance checks</t>
         </is>
       </c>
-      <c r="C24" s="95" t="inlineStr">
+      <c r="C24" s="69" t="n"/>
+      <c r="D24" s="69" t="n"/>
+      <c r="E24" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F24" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D24" s="59" t="n"/>
-      <c r="E24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J24" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L24" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M24" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="G24" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H24" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I24" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K24" s="69" t="n"/>
+      <c r="L24" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M24" s="32" t="n"/>
       <c r="N24" s="32" t="n"/>
       <c r="O24" s="32" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="92" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="A25" s="99" t="n"/>
       <c r="B25" s="93" t="inlineStr">
         <is>
-          <t>Manage scope changes and backlog priorities</t>
+          <t>Deploy the platform to the production environment</t>
         </is>
       </c>
       <c r="C25" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D25" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E25" s="94" t="inlineStr">
+      <c r="D25" s="69" t="n"/>
+      <c r="E25" s="97" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F25" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G25" s="97" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H25" s="94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="96" t="inlineStr">
+      <c r="I25" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G25" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H25" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I25" s="95" t="inlineStr">
+      <c r="J25" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K25" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L25" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K25" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M25" s="32" t="n"/>
       <c r="N25" s="32" t="n"/>
       <c r="O25" s="32" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="98" t="n"/>
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="B26" s="93" t="inlineStr">
         <is>
-          <t>Control quality, defects and adherence to the acceptance criteria</t>
-        </is>
-      </c>
-      <c r="C26" s="95" t="inlineStr">
+          <t>Manage scope changes and backlog priorities</t>
+        </is>
+      </c>
+      <c r="C26" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D26" s="69" t="n"/>
+      <c r="E26" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G26" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H26" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D26" s="59" t="n"/>
-      <c r="E26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I26" s="95" t="inlineStr">
+      <c r="J26" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J26" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L26" s="95" t="inlineStr">
+      <c r="K26" s="69" t="n"/>
+      <c r="L26" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M26" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M26" s="32" t="n"/>
       <c r="N26" s="32" t="n"/>
       <c r="O26" s="32" t="n"/>
     </row>
@@ -3956,73 +3626,65 @@
       <c r="A27" s="98" t="n"/>
       <c r="B27" s="93" t="inlineStr">
         <is>
-          <t>Monitor LLM API costs, quotas and request limits</t>
-        </is>
-      </c>
-      <c r="C27" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D27" s="95" t="inlineStr">
+          <t>Control quality, defects and adherence to the acceptance criteria</t>
+        </is>
+      </c>
+      <c r="C27" s="69" t="n"/>
+      <c r="D27" s="69" t="n"/>
+      <c r="E27" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E27" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G27" s="95" t="inlineStr">
+      <c r="G27" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H27" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I27" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H27" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I27" s="96" t="inlineStr">
+      <c r="J27" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J27" s="59" t="n"/>
-      <c r="K27" s="59" t="n"/>
-      <c r="L27" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M27" s="59" t="n"/>
+      <c r="K27" s="69" t="n"/>
+      <c r="L27" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M27" s="32" t="n"/>
       <c r="N27" s="32" t="n"/>
       <c r="O27" s="32" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="99" t="n"/>
+      <c r="A28" s="98" t="n"/>
       <c r="B28" s="93" t="inlineStr">
         <is>
-          <t>Report project status to the sponsors and the Rector's office</t>
-        </is>
-      </c>
-      <c r="C28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E28" s="97" t="inlineStr">
+          <t>Monitor LLM API costs, quotas and request limits</t>
+        </is>
+      </c>
+      <c r="C28" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" s="69" t="n"/>
+      <c r="E28" s="96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4032,256 +3694,224 @@
           <t>R/A</t>
         </is>
       </c>
-      <c r="G28" s="96" t="inlineStr">
+      <c r="G28" s="69" t="n"/>
+      <c r="H28" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I28" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H28" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J28" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="J28" s="69" t="n"/>
+      <c r="K28" s="69" t="n"/>
+      <c r="L28" s="69" t="n"/>
+      <c r="M28" s="32" t="n"/>
       <c r="N28" s="32" t="n"/>
       <c r="O28" s="32" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="92" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+      <c r="A29" s="99" t="n"/>
       <c r="B29" s="93" t="inlineStr">
         <is>
-          <t>Run the pilot with students and collect feedback</t>
+          <t>Report project status to the sponsors</t>
         </is>
       </c>
       <c r="C29" s="97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D29" s="95" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E29" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F29" s="96" t="inlineStr">
+      <c r="D29" s="97" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E29" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F29" s="94" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G29" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H29" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I29" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J29" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K29" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L29" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M29" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H29" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I29" s="69" t="n"/>
+      <c r="J29" s="69" t="n"/>
+      <c r="K29" s="69" t="n"/>
+      <c r="L29" s="69" t="n"/>
+      <c r="M29" s="32" t="n"/>
       <c r="N29" s="32" t="n"/>
       <c r="O29" s="32" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="98" t="n"/>
+      <c r="A30" s="92" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
       <c r="B30" s="93" t="inlineStr">
         <is>
-          <t>Hand over the system and documentation to the Technical Department and the customer</t>
-        </is>
-      </c>
-      <c r="C30" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D30" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E30" s="96" t="inlineStr">
+          <t>Run the pilot with students and lecturers and collect feedback</t>
+        </is>
+      </c>
+      <c r="C30" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" s="69" t="n"/>
+      <c r="E30" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F30" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G30" s="96" t="inlineStr">
+      <c r="G30" s="95" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="H30" s="96" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I30" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K30" s="69" t="n"/>
+      <c r="L30" s="95" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I30" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J30" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K30" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L30" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M30" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="M30" s="32" t="n"/>
       <c r="N30" s="32" t="n"/>
       <c r="O30" s="32" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="99" t="n"/>
+      <c r="A31" s="98" t="n"/>
       <c r="B31" s="93" t="inlineStr">
         <is>
-          <t>Capture lessons learned and close the project</t>
-        </is>
-      </c>
-      <c r="C31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D31" s="95" t="inlineStr">
+          <t>Hand over the system and documentation to the sponsor</t>
+        </is>
+      </c>
+      <c r="C31" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D31" s="69" t="n"/>
+      <c r="E31" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F31" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G31" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H31" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I31" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J31" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K31" s="97" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G31" s="96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L31" s="97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M31" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="L31" s="69" t="n"/>
+      <c r="M31" s="32" t="n"/>
       <c r="N31" s="32" t="n"/>
       <c r="O31" s="32" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="33" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="32" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="32" t="n"/>
-      <c r="H32" s="32" t="n"/>
-      <c r="I32" s="32" t="n"/>
-      <c r="J32" s="32" t="n"/>
-      <c r="K32" s="32" t="n"/>
-      <c r="L32" s="32" t="n"/>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="99" t="n"/>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>Capture lessons learned and close the project</t>
+        </is>
+      </c>
+      <c r="C32" s="97" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F32" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G32" s="95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H32" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I32" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" s="96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K32" s="69" t="n"/>
+      <c r="L32" s="69" t="n"/>
       <c r="M32" s="32" t="n"/>
       <c r="N32" s="32" t="n"/>
       <c r="O32" s="32" t="n"/>
@@ -4786,17 +4416,17 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A19:A24"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A29:A31"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A25:A28"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A19:A25"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="A13:A18"/>
@@ -4958,16 +4588,18 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="103" t="inlineStr">
         <is>
-          <t>Nataliia
-Shakhovska
-Rector</t>
+          <t>Ministry of
+Education and
+Science (Sponsor)</t>
         </is>
       </c>
       <c r="F4" s="101" t="n"/>
-      <c r="G4" s="101" t="n"/>
-      <c r="H4" s="101" t="n"/>
-      <c r="I4" s="101" t="n"/>
-      <c r="J4" s="101" t="n"/>
+      <c r="G4" s="104" t="inlineStr">
+        <is>
+          <t>Project Manager
+N. Zankovych</t>
+        </is>
+      </c>
       <c r="K4" s="101" t="n"/>
       <c r="L4" s="101" t="n"/>
       <c r="M4" s="101" t="n"/>
@@ -4983,26 +4615,20 @@
       <c r="T4" s="101" t="n"/>
       <c r="U4" s="104" t="inlineStr">
         <is>
-          <t>Nataliia Boiko
-Customer &amp;
-End user</t>
+          <t>Product Owner
+K. Holovskyi</t>
         </is>
       </c>
       <c r="Y4" s="101" t="n"/>
-      <c r="Z4" s="105" t="inlineStr">
-        <is>
-          <t>Technical
-Department of
-Lviv Polytechnic</t>
+      <c r="Z4" s="104" t="inlineStr">
+        <is>
+          <t>Business Analyst
+A. Lysun</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="F5" s="101" t="n"/>
-      <c r="G5" s="101" t="n"/>
-      <c r="H5" s="101" t="n"/>
-      <c r="I5" s="101" t="n"/>
-      <c r="J5" s="101" t="n"/>
       <c r="K5" s="101" t="n"/>
       <c r="L5" s="101" t="n"/>
       <c r="M5" s="101" t="n"/>
@@ -5013,10 +4639,6 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="F6" s="101" t="n"/>
-      <c r="G6" s="101" t="n"/>
-      <c r="H6" s="101" t="n"/>
-      <c r="I6" s="101" t="n"/>
-      <c r="J6" s="101" t="n"/>
       <c r="K6" s="101" t="n"/>
       <c r="L6" s="101" t="n"/>
       <c r="M6" s="101" t="n"/>
@@ -5070,26 +4692,22 @@
       <c r="M8" s="101" t="n"/>
       <c r="N8" s="101" t="n"/>
       <c r="O8" s="101" t="n"/>
-      <c r="P8" s="106" t="inlineStr">
-        <is>
-          <t>Product Owner
-K. Holovskyi</t>
+      <c r="P8" s="104" t="inlineStr">
+        <is>
+          <t>Tech Lead / SWE
+D. Lunhul</t>
         </is>
       </c>
       <c r="T8" s="101" t="n"/>
-      <c r="U8" s="106" t="inlineStr">
-        <is>
-          <t>Project Manager
-N. Zankovych</t>
-        </is>
-      </c>
+      <c r="U8" s="101" t="n"/>
+      <c r="V8" s="101" t="n"/>
+      <c r="W8" s="101" t="n"/>
+      <c r="X8" s="101" t="n"/>
       <c r="Y8" s="101" t="n"/>
-      <c r="Z8" s="106" t="inlineStr">
-        <is>
-          <t>Business Analyst
-A. Lysun</t>
-        </is>
-      </c>
+      <c r="Z8" s="101" t="n"/>
+      <c r="AA8" s="101" t="n"/>
+      <c r="AB8" s="101" t="n"/>
+      <c r="AC8" s="101" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="101" t="n"/>
@@ -5107,7 +4725,15 @@
       <c r="N9" s="101" t="n"/>
       <c r="O9" s="101" t="n"/>
       <c r="T9" s="101" t="n"/>
+      <c r="U9" s="101" t="n"/>
+      <c r="V9" s="101" t="n"/>
+      <c r="W9" s="101" t="n"/>
+      <c r="X9" s="101" t="n"/>
       <c r="Y9" s="101" t="n"/>
+      <c r="Z9" s="101" t="n"/>
+      <c r="AA9" s="101" t="n"/>
+      <c r="AB9" s="101" t="n"/>
+      <c r="AC9" s="101" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="B10" s="101" t="n"/>
@@ -5125,7 +4751,15 @@
       <c r="N10" s="101" t="n"/>
       <c r="O10" s="101" t="n"/>
       <c r="T10" s="101" t="n"/>
+      <c r="U10" s="101" t="n"/>
+      <c r="V10" s="101" t="n"/>
+      <c r="W10" s="101" t="n"/>
+      <c r="X10" s="101" t="n"/>
       <c r="Y10" s="101" t="n"/>
+      <c r="Z10" s="101" t="n"/>
+      <c r="AA10" s="101" t="n"/>
+      <c r="AB10" s="101" t="n"/>
+      <c r="AC10" s="101" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="101" t="n"/>
@@ -5172,12 +4806,10 @@
       <c r="M12" s="101" t="n"/>
       <c r="N12" s="101" t="n"/>
       <c r="O12" s="101" t="n"/>
-      <c r="P12" s="106" t="inlineStr">
-        <is>
-          <t>Tech Lead
-D. Lunhul</t>
-        </is>
-      </c>
+      <c r="P12" s="101" t="n"/>
+      <c r="Q12" s="101" t="n"/>
+      <c r="R12" s="101" t="n"/>
+      <c r="S12" s="101" t="n"/>
       <c r="T12" s="101" t="n"/>
       <c r="U12" s="101" t="n"/>
       <c r="V12" s="101" t="n"/>
@@ -5204,6 +4836,10 @@
       <c r="M13" s="101" t="n"/>
       <c r="N13" s="101" t="n"/>
       <c r="O13" s="101" t="n"/>
+      <c r="P13" s="101" t="n"/>
+      <c r="Q13" s="101" t="n"/>
+      <c r="R13" s="101" t="n"/>
+      <c r="S13" s="101" t="n"/>
       <c r="T13" s="101" t="n"/>
       <c r="U13" s="101" t="n"/>
       <c r="V13" s="101" t="n"/>
@@ -5230,6 +4866,10 @@
       <c r="M14" s="101" t="n"/>
       <c r="N14" s="101" t="n"/>
       <c r="O14" s="101" t="n"/>
+      <c r="P14" s="101" t="n"/>
+      <c r="Q14" s="101" t="n"/>
+      <c r="R14" s="101" t="n"/>
+      <c r="S14" s="101" t="n"/>
       <c r="T14" s="101" t="n"/>
       <c r="U14" s="101" t="n"/>
       <c r="V14" s="101" t="n"/>
@@ -5580,71 +5220,72 @@
       <c r="AC25" s="101" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="103" t="inlineStr">
-        <is>
-          <t>Ministry of
-Education and
-Science (Sponsor)</t>
+      <c r="B26" s="105" t="inlineStr">
+        <is>
+          <t>Technical
+Department of
+Lviv Polytechnic</t>
         </is>
       </c>
       <c r="F26" s="101" t="n"/>
-      <c r="G26" s="101" t="n"/>
-      <c r="H26" s="101" t="n"/>
-      <c r="I26" s="101" t="n"/>
-      <c r="J26" s="101" t="n"/>
+      <c r="G26" s="104" t="inlineStr">
+        <is>
+          <t>DevOps / SWE
+Y. Shevchuk</t>
+        </is>
+      </c>
       <c r="K26" s="101" t="n"/>
-      <c r="L26" s="101" t="n"/>
-      <c r="M26" s="101" t="n"/>
-      <c r="N26" s="101" t="n"/>
-      <c r="O26" s="101" t="n"/>
-      <c r="P26" s="104" t="inlineStr">
+      <c r="L26" s="104" t="inlineStr">
+        <is>
+          <t>QA / SWE
+V. Kamelchuk</t>
+        </is>
+      </c>
+      <c r="P26" s="106" t="inlineStr">
         <is>
           <t>End users —
-students</t>
+students and
+lecturers</t>
         </is>
       </c>
       <c r="T26" s="101" t="n"/>
-      <c r="U26" s="106" t="inlineStr">
-        <is>
-          <t>DevOps
-Y. Shevchuk</t>
-        </is>
-      </c>
+      <c r="U26" s="101" t="n"/>
+      <c r="V26" s="101" t="n"/>
+      <c r="W26" s="101" t="n"/>
+      <c r="X26" s="101" t="n"/>
       <c r="Y26" s="101" t="n"/>
-      <c r="Z26" s="106" t="inlineStr">
-        <is>
-          <t>QA Specialist
-V. Kamelchuk</t>
-        </is>
-      </c>
+      <c r="Z26" s="101" t="n"/>
+      <c r="AA26" s="101" t="n"/>
+      <c r="AB26" s="101" t="n"/>
+      <c r="AC26" s="101" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="F27" s="101" t="n"/>
-      <c r="G27" s="101" t="n"/>
-      <c r="H27" s="101" t="n"/>
-      <c r="I27" s="101" t="n"/>
-      <c r="J27" s="101" t="n"/>
       <c r="K27" s="101" t="n"/>
-      <c r="L27" s="101" t="n"/>
-      <c r="M27" s="101" t="n"/>
-      <c r="N27" s="101" t="n"/>
-      <c r="O27" s="101" t="n"/>
       <c r="T27" s="101" t="n"/>
+      <c r="U27" s="101" t="n"/>
+      <c r="V27" s="101" t="n"/>
+      <c r="W27" s="101" t="n"/>
+      <c r="X27" s="101" t="n"/>
       <c r="Y27" s="101" t="n"/>
+      <c r="Z27" s="101" t="n"/>
+      <c r="AA27" s="101" t="n"/>
+      <c r="AB27" s="101" t="n"/>
+      <c r="AC27" s="101" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="F28" s="101" t="n"/>
-      <c r="G28" s="101" t="n"/>
-      <c r="H28" s="101" t="n"/>
-      <c r="I28" s="101" t="n"/>
-      <c r="J28" s="101" t="n"/>
       <c r="K28" s="101" t="n"/>
-      <c r="L28" s="101" t="n"/>
-      <c r="M28" s="101" t="n"/>
-      <c r="N28" s="101" t="n"/>
-      <c r="O28" s="101" t="n"/>
       <c r="T28" s="101" t="n"/>
+      <c r="U28" s="101" t="n"/>
+      <c r="V28" s="101" t="n"/>
+      <c r="W28" s="101" t="n"/>
+      <c r="X28" s="101" t="n"/>
       <c r="Y28" s="101" t="n"/>
+      <c r="Z28" s="101" t="n"/>
+      <c r="AA28" s="101" t="n"/>
+      <c r="AB28" s="101" t="n"/>
+      <c r="AC28" s="101" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="101" t="n"/>
@@ -6104,21 +5745,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="V1:X2"/>
     <mergeCell ref="F23:H24"/>
     <mergeCell ref="A44:AC44"/>
     <mergeCell ref="F1:H2"/>
-    <mergeCell ref="U8:X10"/>
+    <mergeCell ref="G4:J6"/>
     <mergeCell ref="Z4:AC6"/>
-    <mergeCell ref="Z8:AC10"/>
     <mergeCell ref="B26:E28"/>
-    <mergeCell ref="P12:S14"/>
+    <mergeCell ref="G26:J28"/>
+    <mergeCell ref="L26:O28"/>
     <mergeCell ref="P4:S6"/>
     <mergeCell ref="P26:S28"/>
     <mergeCell ref="B4:E6"/>
-    <mergeCell ref="U26:X28"/>
-    <mergeCell ref="Z26:AC28"/>
     <mergeCell ref="U4:X6"/>
     <mergeCell ref="P8:S10"/>
     <mergeCell ref="A1:A43"/>
